--- a/artfynd/A 3988-2024 artfynd.xlsx
+++ b/artfynd/A 3988-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3988-2024 artfynd.xlsx
+++ b/artfynd/A 3988-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,127 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125184180</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57433</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Alavikmyran, Alavikmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>536541</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7119352</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Agneta Sundkvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Agneta Sundkvist, Hans Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3988-2024 artfynd.xlsx
+++ b/artfynd/A 3988-2024 artfynd.xlsx
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agneta Sundkvist, Hans Andersson</t>
+          <t>Hans Andersson, Agneta Sundkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 3988-2024 artfynd.xlsx
+++ b/artfynd/A 3988-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>125184180</v>
       </c>
       <c r="B3" t="n">
-        <v>57433</v>
+        <v>57585</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Andersson, Agneta Sundkvist</t>
+          <t>Agneta Sundkvist, Hans Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
